--- a/docs/project-import/templates/workos-project-field-sheet-v1.xlsx
+++ b/docs/project-import/templates/workos-project-field-sheet-v1.xlsx
@@ -927,7 +927,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="2">
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
@@ -9072,7 +9071,6 @@
       <c r="N500" s="12" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <autoFilter ref="A5:N500"/>
   <mergeCells count="3">
     <mergeCell ref="A3:N3"/>
@@ -16210,7 +16208,6 @@
       <c r="L500" s="12" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <autoFilter ref="A5:L500"/>
   <mergeCells count="3">
     <mergeCell ref="A3:L3"/>
